--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.21797236540187</v>
+        <v>9.785420509377804</v>
       </c>
       <c r="D2" t="n">
-        <v>59.76978079728384</v>
+        <v>9.712589379558624</v>
       </c>
       <c r="E2" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F2" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.46567937500791</v>
+        <v>8.363172898438785</v>
       </c>
       <c r="D3" t="n">
-        <v>51.38317787334019</v>
+        <v>8.349766404417782</v>
       </c>
       <c r="E3" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F3" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.44429861426465</v>
+        <v>9.984698524818006</v>
       </c>
       <c r="D4" t="n">
-        <v>61.08866279272657</v>
+        <v>9.926907703818069</v>
       </c>
       <c r="E4" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F4" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.41817288053046</v>
+        <v>9.980453093086201</v>
       </c>
       <c r="D5" t="n">
-        <v>61.10379174087485</v>
+        <v>9.929366157892163</v>
       </c>
       <c r="E5" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F5" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.04173218432486</v>
+        <v>9.10678147995279</v>
       </c>
       <c r="D6" t="n">
-        <v>67.59021796897316</v>
+        <v>10.98341041995814</v>
       </c>
       <c r="E6" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F6" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.93315862860764</v>
+        <v>6.001638277148741</v>
       </c>
       <c r="D7" t="n">
-        <v>36.66950492382118</v>
+        <v>5.958794550120942</v>
       </c>
       <c r="E7" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F7" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.59750973353367</v>
+        <v>3.184595331699221</v>
       </c>
       <c r="D8" t="n">
-        <v>19.38343285726934</v>
+        <v>3.149807839306269</v>
       </c>
       <c r="E8" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F8" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.10026668346954</v>
+        <v>2.4537933360638</v>
       </c>
       <c r="D9" t="n">
-        <v>30.71276609938781</v>
+        <v>4.990824491150519</v>
       </c>
       <c r="E9" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F9" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34008727970578</v>
+        <v>3.955264182952189</v>
       </c>
       <c r="D10" t="n">
-        <v>38.45416774482153</v>
+        <v>6.248802258533499</v>
       </c>
       <c r="E10" t="n">
-        <v>18.03910344357084</v>
+        <v>2.931354309580262</v>
       </c>
       <c r="F10" t="n">
-        <v>15.67105178934251</v>
+        <v>2.546545915768158</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
